--- a/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0001T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0001T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.88029053111116</v>
+        <v>5.668047211305563</v>
       </c>
       <c r="D2" t="n">
-        <v>37.03565306718073</v>
+        <v>6.018293623416869</v>
       </c>
       <c r="E2" t="n">
-        <v>7.462391083094852</v>
+        <v>1.212638551002913</v>
       </c>
       <c r="F2" t="n">
-        <v>7.91514429288791</v>
+        <v>1.286210947594285</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.59228220218368</v>
+        <v>3.833745857854848</v>
       </c>
       <c r="D3" t="n">
-        <v>24.12102744007764</v>
+        <v>3.919666959012616</v>
       </c>
       <c r="E3" t="n">
-        <v>7.462391083094852</v>
+        <v>1.212638551002913</v>
       </c>
       <c r="F3" t="n">
-        <v>7.91514429288791</v>
+        <v>1.286210947594285</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.08833227064746</v>
+        <v>3.101853993980213</v>
       </c>
       <c r="D4" t="n">
-        <v>26.46114733708859</v>
+        <v>4.299936442276897</v>
       </c>
       <c r="E4" t="n">
-        <v>7.462391083094852</v>
+        <v>1.212638551002913</v>
       </c>
       <c r="F4" t="n">
-        <v>7.91514429288791</v>
+        <v>1.286210947594285</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.29845035652765</v>
+        <v>3.298498182935742</v>
       </c>
       <c r="D5" t="n">
-        <v>22.59507640331234</v>
+        <v>3.671699915538256</v>
       </c>
       <c r="E5" t="n">
-        <v>7.462391083094852</v>
+        <v>1.212638551002913</v>
       </c>
       <c r="F5" t="n">
-        <v>7.91514429288791</v>
+        <v>1.286210947594285</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.81701415416327</v>
+        <v>3.220264800051532</v>
       </c>
       <c r="D6" t="n">
-        <v>35.03802892969071</v>
+        <v>5.693679701074741</v>
       </c>
       <c r="E6" t="n">
-        <v>7.462391083094852</v>
+        <v>1.212638551002913</v>
       </c>
       <c r="F6" t="n">
-        <v>7.91514429288791</v>
+        <v>1.286210947594285</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>13.03566456125063</v>
+        <v>2.118295491203228</v>
       </c>
       <c r="D7" t="n">
-        <v>15.96090796360168</v>
+        <v>2.593647544085273</v>
       </c>
       <c r="E7" t="n">
-        <v>7.462391083094852</v>
+        <v>1.212638551002913</v>
       </c>
       <c r="F7" t="n">
-        <v>7.91514429288791</v>
+        <v>1.286210947594285</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>6.073483837472223</v>
+        <v>0.9869411235892362</v>
       </c>
       <c r="D8" t="n">
-        <v>25.13798924365189</v>
+        <v>4.084923252093432</v>
       </c>
       <c r="E8" t="n">
-        <v>7.462391083094852</v>
+        <v>1.212638551002913</v>
       </c>
       <c r="F8" t="n">
-        <v>7.91514429288791</v>
+        <v>1.286210947594285</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>14.46868252975009</v>
+        <v>2.35116091108439</v>
       </c>
       <c r="D9" t="n">
-        <v>14.79875485607616</v>
+        <v>2.404797664112376</v>
       </c>
       <c r="E9" t="n">
-        <v>7.462391083094852</v>
+        <v>1.212638551002913</v>
       </c>
       <c r="F9" t="n">
-        <v>7.91514429288791</v>
+        <v>1.286210947594285</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>9.333491545581557</v>
+        <v>1.516692376157003</v>
       </c>
       <c r="D10" t="n">
-        <v>10.18540218753116</v>
+        <v>1.655127855473813</v>
       </c>
       <c r="E10" t="n">
-        <v>7.462391083094852</v>
+        <v>1.212638551002913</v>
       </c>
       <c r="F10" t="n">
-        <v>7.91514429288791</v>
+        <v>1.286210947594285</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>12.43196977919038</v>
+        <v>2.020195089118437</v>
       </c>
       <c r="D11" t="n">
-        <v>21.78636674485286</v>
+        <v>3.54028459603859</v>
       </c>
       <c r="E11" t="n">
-        <v>7.462391083094852</v>
+        <v>1.212638551002913</v>
       </c>
       <c r="F11" t="n">
-        <v>7.91514429288791</v>
+        <v>1.286210947594285</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>12.57054679297429</v>
+        <v>2.042713853858323</v>
       </c>
       <c r="D12" t="n">
-        <v>12.34425471326961</v>
+        <v>2.005941390906312</v>
       </c>
       <c r="E12" t="n">
-        <v>7.462391083094852</v>
+        <v>1.212638551002913</v>
       </c>
       <c r="F12" t="n">
-        <v>7.91514429288791</v>
+        <v>1.286210947594285</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>23.58524421568647</v>
+        <v>3.832602185049052</v>
       </c>
       <c r="D13" t="n">
-        <v>23.37511018030141</v>
+        <v>3.79845540429898</v>
       </c>
       <c r="E13" t="n">
-        <v>7.462391083094852</v>
+        <v>1.212638551002913</v>
       </c>
       <c r="F13" t="n">
-        <v>7.91514429288791</v>
+        <v>1.286210947594285</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
